--- a/public/template-importazione.xlsx
+++ b/public/template-importazione.xlsx
@@ -877,7 +877,7 @@
         <v>2026-04-25</v>
       </c>
       <c r="D4" t="str">
-        <v>chiusura</v>
+        <v>vacanza</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Tipo: vacanza | chiusura | assenza</v>
+        <v>Tipo: vacanza | congedo | malattia</v>
       </c>
     </row>
   </sheetData>
